--- a/06_optimizers/excel_optimizers_demo.xlsx
+++ b/06_optimizers/excel_optimizers_demo.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -72,8 +72,16 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F2937"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -100,8 +108,23 @@
         <fgColor rgb="00FFF7CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F4EF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002F6F9F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -137,11 +160,25 @@
         <color rgb="00D6B656"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9E2EF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9E2EF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9E2EF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9E2EF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -196,6 +233,30 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -565,7 +626,7 @@
   <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="74" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -580,7 +641,7 @@
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>ExcelをUIにして、外部PythonがWorkbookの値を読み、計算結果をDataFrameで返します。</t>
+          <t>同じ勾配列を、SGD、Momentum、AdaGrad、RMSProp、Adamで更新したときの違いを確認します。</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -612,7 +673,7 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>今回のゴール</t>
+          <t>01_INPUT の gradient、learning_rate、momentum、rms_decay、beta1、beta2、epsilon、display_mode を変更してPythonを再実行します。</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
@@ -624,7 +685,7 @@
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>Pythonが読む範囲</t>
+          <t>display_mode は compare / state / summary / exam から選びます。</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
@@ -656,18 +717,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
           <t>第6回 最適化手法: 入力と設定</t>
@@ -679,10 +740,10 @@
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
     </row>
-    <row r="2">
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>このシートの表をPythonが xl(...) で読みます。値や設定を変えて結果の変化を確認します。</t>
+          <t>このシートの表をPythonが xl(...) で読みます。勾配列や設定を変えて、手法ごとの更新量の違いを確認します。</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -691,7 +752,7 @@
       <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n"/>
     </row>
-    <row r="3">
+    <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="n"/>
       <c r="B3" s="2" t="n"/>
       <c r="C3" s="2" t="n"/>
@@ -699,15 +760,15 @@
       <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n"/>
     </row>
-    <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>勾配列</t>
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="2" t="n"/>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>最適化設定</t>
         </is>
@@ -715,7 +776,7 @@
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
     </row>
-    <row r="5">
+    <row r="5" ht="22" customHeight="1">
       <c r="A5" s="2" t="n"/>
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="n"/>
@@ -723,164 +784,180 @@
       <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="n"/>
     </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>step</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>gradient</t>
         </is>
       </c>
       <c r="C6" s="2" t="n"/>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>setting</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="14" t="n">
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="14" t="n">
+      <c r="B7" s="21" t="n">
         <v>0.8</v>
       </c>
       <c r="C7" s="2" t="n"/>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>display_mode</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>compare</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
-        <is>
-          <t>リストから選択: compare / state / exam</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="n">
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>リストから選択: compare / state / summary / exam</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="14" t="n">
+      <c r="B8" s="21" t="n">
         <v>0.5</v>
       </c>
       <c r="C8" s="2" t="n"/>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>learning_rate</t>
         </is>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="24" t="n">
         <v>0.1</v>
       </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>学習率</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="14" t="n">
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="14" t="n">
+      <c r="B9" s="21" t="n">
         <v>-0.2</v>
       </c>
       <c r="C9" s="2" t="n"/>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>momentum</t>
         </is>
       </c>
-      <c r="E9" s="14" t="n">
+      <c r="E9" s="24" t="n">
         <v>0.9</v>
       </c>
-      <c r="F9" s="14" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>Momentum係数</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="14" t="n">
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="14" t="n">
+      <c r="B10" s="21" t="n">
         <v>0.1</v>
       </c>
       <c r="C10" s="2" t="n"/>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>beta1</t>
-        </is>
-      </c>
-      <c r="E10" s="14" t="n">
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>rms_decay</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="n">
         <v>0.9</v>
       </c>
-      <c r="F10" s="14" t="inlineStr">
-        <is>
-          <t>Adam一次</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>RMSPropの移動平均係数</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
       <c r="A11" s="2" t="n"/>
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="n"/>
-      <c r="D11" s="14" t="inlineStr">
-        <is>
-          <t>beta2</t>
-        </is>
-      </c>
-      <c r="E11" s="14" t="n">
-        <v>0.999</v>
-      </c>
-      <c r="F11" s="14" t="inlineStr">
-        <is>
-          <t>Adam二次</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>beta1</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>Adam一次</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
       <c r="A12" s="2" t="n"/>
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="2" t="n"/>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>beta2</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>Adam二次</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="D13" s="25" t="inlineStr">
         <is>
           <t>epsilon</t>
         </is>
       </c>
-      <c r="E12" s="14" t="n">
+      <c r="E13" s="26" t="n">
         <v>1e-08</v>
       </c>
-      <c r="F12" s="14" t="inlineStr">
+      <c r="F13" s="25" t="inlineStr">
         <is>
           <t>ゼロ割回避</t>
         </is>
       </c>
     </row>
+    <row r="14" ht="22" customHeight="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="リストから選択してください" error="このセルは手入力ではなく、右側のリストから選択します。" promptTitle="選択式の設定" prompt="候補から選ぶと、Pythonの返す表や計算条件が切り替わります。" type="list">
-      <formula1>"compare,state,exam"</formula1>
+    <dataValidation sqref="E7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"compare,state,summary,exam"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -897,7 +974,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="78" customWidth="1" min="2" max="2"/>
+    <col width="92" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -911,7 +988,7 @@
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>このシートはPython in Excelの実行手順だけを置きます。概念説明はスライドとREADMEで確認します。</t>
+          <t>このシートは実行手順だけを置きます。概念説明はスライドとREADMEで確認します。</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -974,7 +1051,7 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>01_INPUT の値や display_mode を変えて再実行する</t>
+          <t>01_INPUT の display_mode を compare / state / summary / exam に変えて再実行する</t>
         </is>
       </c>
     </row>
